--- a/logisticreg/logsticreg_sample.xlsx
+++ b/logisticreg/logsticreg_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4da35acd1e075fc6/R/semi_lesson/logisticreg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{DFEA6285-55E2-DA43-B129-7BF1103B32D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9197EF85-5D84-BC4E-AEC7-46E4AA465B38}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{DFEA6285-55E2-DA43-B129-7BF1103B32D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACAF997-236D-7A40-8067-A64704BBE67D}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1760" windowWidth="28300" windowHeight="17440" xr2:uid="{B55817BE-B131-424D-8EE5-985CD1DD88B4}"/>
   </bookViews>
@@ -437,12 +437,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1967,8 +1967,8 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>5</v>
+        <f t="shared" ref="E59:E101" ca="1" si="0">RANDBETWEEN(4,7)</f>
+        <v>4</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -1994,8 +1994,8 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
       <c r="F61">
@@ -2048,8 +2048,8 @@
         <v>1</v>
       </c>
       <c r="E62">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2075,8 +2075,8 @@
         <v>2</v>
       </c>
       <c r="E63">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="E64">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
       <c r="F64">
@@ -2129,8 +2129,8 @@
         <v>2</v>
       </c>
       <c r="E65">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2156,8 +2156,8 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2183,8 +2183,8 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -2210,8 +2210,8 @@
         <v>2</v>
       </c>
       <c r="E68">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
       <c r="E69">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="F69">
@@ -2264,8 +2264,8 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2291,8 +2291,8 @@
         <v>2</v>
       </c>
       <c r="E71">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2318,8 +2318,8 @@
         <v>2</v>
       </c>
       <c r="E72">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="F73">
@@ -2372,8 +2372,8 @@
         <v>2</v>
       </c>
       <c r="E74">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2399,8 +2399,8 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2426,8 +2426,8 @@
         <v>2</v>
       </c>
       <c r="E76">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="F77">
@@ -2480,8 +2480,8 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2507,8 +2507,8 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2534,8 +2534,8 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -2561,8 +2561,8 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2588,8 +2588,8 @@
         <v>2</v>
       </c>
       <c r="E82">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -2615,8 +2615,8 @@
         <v>2</v>
       </c>
       <c r="E83">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2642,8 +2642,8 @@
         <v>2</v>
       </c>
       <c r="E84">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="E85">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="F85">
@@ -2696,8 +2696,8 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -2723,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="E87">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
       <c r="F87">
@@ -2750,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="E88">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
       <c r="F88">
@@ -2777,8 +2777,8 @@
         <v>2</v>
       </c>
       <c r="E89">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -2804,8 +2804,8 @@
         <v>2</v>
       </c>
       <c r="E90">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -2831,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="F91">
@@ -2858,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="E92">
-        <f ca="1">RANDBETWEEN(4,7)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="F92">
@@ -2885,8 +2885,8 @@
         <v>1</v>
       </c>
       <c r="E93">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -2912,8 +2912,8 @@
         <v>2</v>
       </c>
       <c r="E94">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -2939,8 +2939,8 @@
         <v>2</v>
       </c>
       <c r="E95">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -2966,8 +2966,8 @@
         <v>2</v>
       </c>
       <c r="E96">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -2993,8 +2993,8 @@
         <v>2</v>
       </c>
       <c r="E97">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -3020,8 +3020,8 @@
         <v>2</v>
       </c>
       <c r="E98">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -3047,8 +3047,8 @@
         <v>1</v>
       </c>
       <c r="E99">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -3074,8 +3074,8 @@
         <v>2</v>
       </c>
       <c r="E100">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -3101,8 +3101,8 @@
         <v>2</v>
       </c>
       <c r="E101">
-        <f ca="1">RANDBETWEEN(4,7)</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="F101">
         <v>1</v>
